--- a/Excel9to10/Day-5.xlsx
+++ b/Excel9to10/Day-5.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AllData\Excel9to10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639B58B6-9AAF-4444-A611-ADEEC54A3075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF1EF0E-4879-4250-BE17-010C4E0CC127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{647DEF58-673A-4D42-A1E9-37071E949B6C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{647DEF58-673A-4D42-A1E9-37071E949B6C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,12 +30,37 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="129">
   <si>
     <t>ID</t>
   </si>
@@ -479,11 +505,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -502,9 +529,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -542,7 +569,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -648,7 +675,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -790,7 +817,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -798,21 +825,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F125F0B-8C0C-45C0-923A-98B0C145109C}">
-  <dimension ref="A1:V101"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:W101"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.88671875" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" customWidth="1"/>
-    <col min="10" max="10" width="10.33203125" customWidth="1"/>
-    <col min="12" max="14" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.85546875" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" customWidth="1"/>
+    <col min="12" max="14" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" customWidth="1"/>
     <col min="18" max="18" width="17" customWidth="1"/>
-    <col min="22" max="22" width="11.6640625" customWidth="1"/>
+    <col min="22" max="22" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -844,7 +871,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -876,7 +903,7 @@
         <v>3480</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -908,7 +935,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -949,7 +976,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -981,16 +1008,10 @@
         <v>3660</v>
       </c>
       <c r="L5" s="1"/>
-      <c r="M5" s="1" t="str">
-        <f>IFERROR(INDEX(B:B,MATCH(L5,A:A,0)),"-")</f>
-        <v>-</v>
-      </c>
-      <c r="N5" s="1" t="str">
-        <f>IFERROR(INDEX(E:E,MATCH(L5,A:A,0)),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1022,7 +1043,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1054,7 +1075,7 @@
         <v>3240</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1086,7 +1107,7 @@
         <v>5600</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1148,7 +1169,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1180,46 +1201,46 @@
         <v>3600</v>
       </c>
       <c r="M10">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N10" t="str">
-        <f>VLOOKUP($M$10,$A$2:$J$101,2,FALSE)</f>
-        <v>Sarah Lee</v>
+        <f>_xlfn.XLOOKUP($M$10,$A$2:$A$101,B2:B101,"-")</f>
+        <v>Isabella Martinez</v>
       </c>
       <c r="O10" t="str">
-        <f>VLOOKUP($M$10,$A$2:$J$101,3,FALSE)</f>
+        <f>_xlfn.XLOOKUP($M$10,$A$2:$A$101,C2:C101,"-")</f>
         <v>HR</v>
       </c>
       <c r="P10" t="str">
-        <f>VLOOKUP($M$10,$A$2:$J$101,4,FALSE)</f>
+        <f t="shared" ref="P10:V10" si="0">_xlfn.XLOOKUP($M$10,$A$2:$A$101,D2:D101,"-")</f>
         <v>Chicago</v>
       </c>
       <c r="Q10">
-        <f>VLOOKUP($M$10,$A$2:$J$101,5,FALSE)</f>
-        <v>52000</v>
+        <f t="shared" si="0"/>
+        <v>51000</v>
       </c>
       <c r="R10">
-        <f>VLOOKUP($M$10,$A$2:$J$101,6,FALSE)</f>
-        <v>43647</v>
+        <f t="shared" si="0"/>
+        <v>43645</v>
       </c>
       <c r="S10" t="str">
-        <f>VLOOKUP($M$10,$A$2:$J$101,7,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>David</v>
       </c>
       <c r="T10">
-        <f>VLOOKUP($M$10,$A$2:$J$101,8,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="U10">
-        <f>VLOOKUP($M$10,$A$2:$J$101,9,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="V10">
-        <f>VLOOKUP($M$10,$A$2:$J$101,10,FALSE)</f>
-        <v>2600</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1251,7 +1272,7 @@
         <v>5840</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1283,7 +1304,7 @@
         <v>3420</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1314,8 +1335,12 @@
       <c r="J13" s="1">
         <v>2500</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="L13">
+        <f>_xlfn.MODE.SNGL(E2:E101)</f>
+        <v>71000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1346,12 +1371,8 @@
       <c r="J14" s="1">
         <v>5520</v>
       </c>
-      <c r="M14">
-        <f>MATCH(L15,G2:G15,0)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1382,12 +1403,14 @@
       <c r="J15" s="1">
         <v>3720</v>
       </c>
-      <c r="L15" t="str">
-        <f>INDEX(G2:G15,3)</f>
-        <v>Karen</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="N15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1419,7 +1442,7 @@
         <v>3550</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1451,7 +1474,7 @@
         <v>3360</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1482,8 +1505,39 @@
       <c r="J18" s="1">
         <v>5640</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N18" cm="1">
+        <f t="array" ref="N18:W37">_xlfn._xlws.FILTER(A1:J101,D1:D101=O15,"-")</f>
+        <v>2</v>
+      </c>
+      <c r="O18" t="str">
+        <v>Sarah Lee</v>
+      </c>
+      <c r="P18" t="str">
+        <v>HR</v>
+      </c>
+      <c r="Q18" t="str">
+        <v>Chicago</v>
+      </c>
+      <c r="R18">
+        <v>52000</v>
+      </c>
+      <c r="S18">
+        <v>43647</v>
+      </c>
+      <c r="T18" t="str">
+        <v>David</v>
+      </c>
+      <c r="U18">
+        <v>3</v>
+      </c>
+      <c r="V18">
+        <v>5</v>
+      </c>
+      <c r="W18">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1514,8 +1568,38 @@
       <c r="J19" s="1">
         <v>2575</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N19">
+        <v>8</v>
+      </c>
+      <c r="O19" t="str">
+        <v>Isabella Martinez</v>
+      </c>
+      <c r="P19" t="str">
+        <v>HR</v>
+      </c>
+      <c r="Q19" t="str">
+        <v>Chicago</v>
+      </c>
+      <c r="R19">
+        <v>51000</v>
+      </c>
+      <c r="S19">
+        <v>43645</v>
+      </c>
+      <c r="T19" t="str">
+        <v>David</v>
+      </c>
+      <c r="U19">
+        <v>3</v>
+      </c>
+      <c r="V19">
+        <v>5</v>
+      </c>
+      <c r="W19">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1546,8 +1630,41 @@
       <c r="J20" s="1">
         <v>3630</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L20" s="4">
+        <v>46058</v>
+      </c>
+      <c r="N20">
+        <v>12</v>
+      </c>
+      <c r="O20" t="str">
+        <v>Mia Walker</v>
+      </c>
+      <c r="P20" t="str">
+        <v>HR</v>
+      </c>
+      <c r="Q20" t="str">
+        <v>Chicago</v>
+      </c>
+      <c r="R20">
+        <v>50000</v>
+      </c>
+      <c r="S20">
+        <v>44025</v>
+      </c>
+      <c r="T20" t="str">
+        <v>David</v>
+      </c>
+      <c r="U20">
+        <v>3</v>
+      </c>
+      <c r="V20">
+        <v>5</v>
+      </c>
+      <c r="W20">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1578,8 +1695,38 @@
       <c r="J21" s="1">
         <v>5880</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N21">
+        <v>18</v>
+      </c>
+      <c r="O21" t="str">
+        <v>Evelyn Wright</v>
+      </c>
+      <c r="P21" t="str">
+        <v>HR</v>
+      </c>
+      <c r="Q21" t="str">
+        <v>Chicago</v>
+      </c>
+      <c r="R21">
+        <v>51500</v>
+      </c>
+      <c r="S21">
+        <v>43739</v>
+      </c>
+      <c r="T21" t="str">
+        <v>David</v>
+      </c>
+      <c r="U21">
+        <v>3</v>
+      </c>
+      <c r="V21">
+        <v>5</v>
+      </c>
+      <c r="W21">
+        <v>2575</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1610,8 +1757,38 @@
       <c r="J22" s="1">
         <v>3510</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N22">
+        <v>22</v>
+      </c>
+      <c r="O22" t="str">
+        <v>Amelia Green</v>
+      </c>
+      <c r="P22" t="str">
+        <v>HR</v>
+      </c>
+      <c r="Q22" t="str">
+        <v>Chicago</v>
+      </c>
+      <c r="R22">
+        <v>52500</v>
+      </c>
+      <c r="S22">
+        <v>43511</v>
+      </c>
+      <c r="T22" t="str">
+        <v>David</v>
+      </c>
+      <c r="U22">
+        <v>3</v>
+      </c>
+      <c r="V22">
+        <v>5</v>
+      </c>
+      <c r="W22">
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1642,8 +1819,38 @@
       <c r="J23" s="1">
         <v>2625</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N23">
+        <v>28</v>
+      </c>
+      <c r="O23" t="str">
+        <v>Elizabeth Turner</v>
+      </c>
+      <c r="P23" t="str">
+        <v>HR</v>
+      </c>
+      <c r="Q23" t="str">
+        <v>Chicago</v>
+      </c>
+      <c r="R23">
+        <v>50500</v>
+      </c>
+      <c r="S23">
+        <v>43655</v>
+      </c>
+      <c r="T23" t="str">
+        <v>David</v>
+      </c>
+      <c r="U23">
+        <v>3</v>
+      </c>
+      <c r="V23">
+        <v>5</v>
+      </c>
+      <c r="W23">
+        <v>2525</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1674,8 +1881,38 @@
       <c r="J24" s="1">
         <v>5400</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N24">
+        <v>32</v>
+      </c>
+      <c r="O24" t="str">
+        <v>Sofia Evans</v>
+      </c>
+      <c r="P24" t="str">
+        <v>HR</v>
+      </c>
+      <c r="Q24" t="str">
+        <v>Chicago</v>
+      </c>
+      <c r="R24">
+        <v>53000</v>
+      </c>
+      <c r="S24">
+        <v>44079</v>
+      </c>
+      <c r="T24" t="str">
+        <v>David</v>
+      </c>
+      <c r="U24">
+        <v>3</v>
+      </c>
+      <c r="V24">
+        <v>5</v>
+      </c>
+      <c r="W24">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1706,8 +1943,38 @@
       <c r="J25" s="1">
         <v>3690</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N25">
+        <v>38</v>
+      </c>
+      <c r="O25" t="str">
+        <v>Grace Rogers</v>
+      </c>
+      <c r="P25" t="str">
+        <v>HR</v>
+      </c>
+      <c r="Q25" t="str">
+        <v>Chicago</v>
+      </c>
+      <c r="R25">
+        <v>52000</v>
+      </c>
+      <c r="S25">
+        <v>43627</v>
+      </c>
+      <c r="T25" t="str">
+        <v>David</v>
+      </c>
+      <c r="U25">
+        <v>3</v>
+      </c>
+      <c r="V25">
+        <v>5</v>
+      </c>
+      <c r="W25">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1738,8 +2005,38 @@
       <c r="J26" s="1">
         <v>3625</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N26">
+        <v>42</v>
+      </c>
+      <c r="O26" t="str">
+        <v>Hazel Bell</v>
+      </c>
+      <c r="P26" t="str">
+        <v>HR</v>
+      </c>
+      <c r="Q26" t="str">
+        <v>Chicago</v>
+      </c>
+      <c r="R26">
+        <v>53500</v>
+      </c>
+      <c r="S26">
+        <v>43669</v>
+      </c>
+      <c r="T26" t="str">
+        <v>David</v>
+      </c>
+      <c r="U26">
+        <v>3</v>
+      </c>
+      <c r="V26">
+        <v>5</v>
+      </c>
+      <c r="W26">
+        <v>2675</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1770,8 +2067,38 @@
       <c r="J27" s="1">
         <v>3270</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N27">
+        <v>48</v>
+      </c>
+      <c r="O27" t="str">
+        <v>Nora Cox</v>
+      </c>
+      <c r="P27" t="str">
+        <v>HR</v>
+      </c>
+      <c r="Q27" t="str">
+        <v>Chicago</v>
+      </c>
+      <c r="R27">
+        <v>51000</v>
+      </c>
+      <c r="S27">
+        <v>43696</v>
+      </c>
+      <c r="T27" t="str">
+        <v>David</v>
+      </c>
+      <c r="U27">
+        <v>3</v>
+      </c>
+      <c r="V27">
+        <v>5</v>
+      </c>
+      <c r="W27">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1802,8 +2129,38 @@
       <c r="J28" s="1">
         <v>5560</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N28">
+        <v>52</v>
+      </c>
+      <c r="O28" t="str">
+        <v>Penelope Torres</v>
+      </c>
+      <c r="P28" t="str">
+        <v>HR</v>
+      </c>
+      <c r="Q28" t="str">
+        <v>Chicago</v>
+      </c>
+      <c r="R28">
+        <v>54000</v>
+      </c>
+      <c r="S28">
+        <v>43600</v>
+      </c>
+      <c r="T28" t="str">
+        <v>David</v>
+      </c>
+      <c r="U28">
+        <v>3</v>
+      </c>
+      <c r="V28">
+        <v>5</v>
+      </c>
+      <c r="W28">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1834,8 +2191,38 @@
       <c r="J29" s="1">
         <v>2525</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N29">
+        <v>58</v>
+      </c>
+      <c r="O29" t="str">
+        <v>Eleanor Foster</v>
+      </c>
+      <c r="P29" t="str">
+        <v>HR</v>
+      </c>
+      <c r="Q29" t="str">
+        <v>Chicago</v>
+      </c>
+      <c r="R29">
+        <v>51500</v>
+      </c>
+      <c r="S29">
+        <v>43726</v>
+      </c>
+      <c r="T29" t="str">
+        <v>David</v>
+      </c>
+      <c r="U29">
+        <v>3</v>
+      </c>
+      <c r="V29">
+        <v>5</v>
+      </c>
+      <c r="W29">
+        <v>2575</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1866,8 +2253,38 @@
       <c r="J30" s="1">
         <v>3660</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N30">
+        <v>62</v>
+      </c>
+      <c r="O30" t="str">
+        <v>Lucy Rivera</v>
+      </c>
+      <c r="P30" t="str">
+        <v>HR</v>
+      </c>
+      <c r="Q30" t="str">
+        <v>Chicago</v>
+      </c>
+      <c r="R30">
+        <v>53000</v>
+      </c>
+      <c r="S30">
+        <v>43704</v>
+      </c>
+      <c r="T30" t="str">
+        <v>David</v>
+      </c>
+      <c r="U30">
+        <v>3</v>
+      </c>
+      <c r="V30">
+        <v>5</v>
+      </c>
+      <c r="W30">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1898,8 +2315,38 @@
       <c r="J31" s="1">
         <v>5920</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N31">
+        <v>68</v>
+      </c>
+      <c r="O31" t="str">
+        <v>Eva Coleman</v>
+      </c>
+      <c r="P31" t="str">
+        <v>HR</v>
+      </c>
+      <c r="Q31" t="str">
+        <v>Chicago</v>
+      </c>
+      <c r="R31">
+        <v>50500</v>
+      </c>
+      <c r="S31">
+        <v>43740</v>
+      </c>
+      <c r="T31" t="str">
+        <v>David</v>
+      </c>
+      <c r="U31">
+        <v>3</v>
+      </c>
+      <c r="V31">
+        <v>5</v>
+      </c>
+      <c r="W31">
+        <v>2525</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1930,8 +2377,38 @@
       <c r="J32" s="1">
         <v>3450</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N32">
+        <v>72</v>
+      </c>
+      <c r="O32" t="str">
+        <v>Lillian Patterson</v>
+      </c>
+      <c r="P32" t="str">
+        <v>HR</v>
+      </c>
+      <c r="Q32" t="str">
+        <v>Chicago</v>
+      </c>
+      <c r="R32">
+        <v>51500</v>
+      </c>
+      <c r="S32">
+        <v>43625</v>
+      </c>
+      <c r="T32" t="str">
+        <v>David</v>
+      </c>
+      <c r="U32">
+        <v>3</v>
+      </c>
+      <c r="V32">
+        <v>5</v>
+      </c>
+      <c r="W32">
+        <v>2575</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1962,8 +2439,38 @@
       <c r="J33" s="1">
         <v>2650</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N33">
+        <v>78</v>
+      </c>
+      <c r="O33" t="str">
+        <v>Bella Hughes</v>
+      </c>
+      <c r="P33" t="str">
+        <v>HR</v>
+      </c>
+      <c r="Q33" t="str">
+        <v>Chicago</v>
+      </c>
+      <c r="R33">
+        <v>52000</v>
+      </c>
+      <c r="S33">
+        <v>43711</v>
+      </c>
+      <c r="T33" t="str">
+        <v>David</v>
+      </c>
+      <c r="U33">
+        <v>3</v>
+      </c>
+      <c r="V33">
+        <v>5</v>
+      </c>
+      <c r="W33">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1994,8 +2501,38 @@
       <c r="J34" s="1">
         <v>5440</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N34">
+        <v>82</v>
+      </c>
+      <c r="O34" t="str">
+        <v>Clara Rivera</v>
+      </c>
+      <c r="P34" t="str">
+        <v>HR</v>
+      </c>
+      <c r="Q34" t="str">
+        <v>Chicago</v>
+      </c>
+      <c r="R34">
+        <v>53000</v>
+      </c>
+      <c r="S34">
+        <v>43665</v>
+      </c>
+      <c r="T34" t="str">
+        <v>David</v>
+      </c>
+      <c r="U34">
+        <v>3</v>
+      </c>
+      <c r="V34">
+        <v>5</v>
+      </c>
+      <c r="W34">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -2026,8 +2563,38 @@
       <c r="J35" s="1">
         <v>3750</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N35">
+        <v>88</v>
+      </c>
+      <c r="O35" t="str">
+        <v>Sadie Henderson</v>
+      </c>
+      <c r="P35" t="str">
+        <v>HR</v>
+      </c>
+      <c r="Q35" t="str">
+        <v>Chicago</v>
+      </c>
+      <c r="R35">
+        <v>51000</v>
+      </c>
+      <c r="S35">
+        <v>43637</v>
+      </c>
+      <c r="T35" t="str">
+        <v>David</v>
+      </c>
+      <c r="U35">
+        <v>3</v>
+      </c>
+      <c r="V35">
+        <v>5</v>
+      </c>
+      <c r="W35">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -2058,8 +2625,38 @@
       <c r="J36" s="1">
         <v>3575</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N36">
+        <v>92</v>
+      </c>
+      <c r="O36" t="str">
+        <v>Nora Reynolds</v>
+      </c>
+      <c r="P36" t="str">
+        <v>HR</v>
+      </c>
+      <c r="Q36" t="str">
+        <v>Chicago</v>
+      </c>
+      <c r="R36">
+        <v>52500</v>
+      </c>
+      <c r="S36">
+        <v>43682</v>
+      </c>
+      <c r="T36" t="str">
+        <v>David</v>
+      </c>
+      <c r="U36">
+        <v>3</v>
+      </c>
+      <c r="V36">
+        <v>5</v>
+      </c>
+      <c r="W36">
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -2090,8 +2687,38 @@
       <c r="J37" s="1">
         <v>3300</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="N37">
+        <v>98</v>
+      </c>
+      <c r="O37" t="str">
+        <v>Maya Graham</v>
+      </c>
+      <c r="P37" t="str">
+        <v>HR</v>
+      </c>
+      <c r="Q37" t="str">
+        <v>Chicago</v>
+      </c>
+      <c r="R37">
+        <v>50500</v>
+      </c>
+      <c r="S37">
+        <v>43632</v>
+      </c>
+      <c r="T37" t="str">
+        <v>David</v>
+      </c>
+      <c r="U37">
+        <v>3</v>
+      </c>
+      <c r="V37">
+        <v>5</v>
+      </c>
+      <c r="W37">
+        <v>2525</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -2123,7 +2750,7 @@
         <v>5680</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -2155,7 +2782,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -2187,7 +2814,7 @@
         <v>3630</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -2219,7 +2846,7 @@
         <v>5960</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -2251,7 +2878,7 @@
         <v>3390</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -2283,7 +2910,7 @@
         <v>2675</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -2315,7 +2942,7 @@
         <v>5480</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -2347,7 +2974,7 @@
         <v>3780</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -2379,7 +3006,7 @@
         <v>3525</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -2411,7 +3038,7 @@
         <v>3330</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -2443,7 +3070,7 @@
         <v>5720</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -2475,7 +3102,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -2507,7 +3134,7 @@
         <v>3690</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -2539,7 +3166,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -2571,7 +3198,7 @@
         <v>3540</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -2603,7 +3230,7 @@
         <v>2700</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -2635,7 +3262,7 @@
         <v>5560</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -2667,7 +3294,7 @@
         <v>3810</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -2699,7 +3326,7 @@
         <v>3550</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -2731,7 +3358,7 @@
         <v>3360</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -2763,7 +3390,7 @@
         <v>5640</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -2795,7 +3422,7 @@
         <v>2575</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -2827,7 +3454,7 @@
         <v>3720</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -2859,7 +3486,7 @@
         <v>6040</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -2891,7 +3518,7 @@
         <v>3510</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -2923,7 +3550,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -2955,7 +3582,7 @@
         <v>5600</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -2987,7 +3614,7 @@
         <v>3840</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -3019,7 +3646,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -3051,7 +3678,7 @@
         <v>3270</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -3083,7 +3710,7 @@
         <v>5680</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -3115,7 +3742,7 @@
         <v>2525</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -3147,7 +3774,7 @@
         <v>3750</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -3179,7 +3806,7 @@
         <v>6080</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -3211,7 +3838,7 @@
         <v>3420</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -3243,7 +3870,7 @@
         <v>2575</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -3275,7 +3902,7 @@
         <v>5520</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -3307,7 +3934,7 @@
         <v>3690</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -3339,7 +3966,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -3371,7 +3998,7 @@
         <v>3300</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -3403,7 +4030,7 @@
         <v>5600</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -3435,7 +4062,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -3467,7 +4094,7 @@
         <v>3660</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -3499,7 +4126,7 @@
         <v>5920</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -3531,7 +4158,7 @@
         <v>3480</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -3563,7 +4190,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -3595,7 +4222,7 @@
         <v>5640</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -3627,7 +4254,7 @@
         <v>3750</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -3659,7 +4286,7 @@
         <v>3575</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -3691,7 +4318,7 @@
         <v>3330</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -3723,7 +4350,7 @@
         <v>5680</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -3755,7 +4382,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -3787,7 +4414,7 @@
         <v>3720</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -3819,7 +4446,7 @@
         <v>6040</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -3851,7 +4478,7 @@
         <v>3450</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -3883,7 +4510,7 @@
         <v>2625</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -3915,7 +4542,7 @@
         <v>5560</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -3947,7 +4574,7 @@
         <v>3780</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -3979,7 +4606,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -4011,7 +4638,7 @@
         <v>3270</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -4043,7 +4670,7 @@
         <v>5720</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -4075,7 +4702,7 @@
         <v>2525</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -4107,7 +4734,7 @@
         <v>3690</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -4140,7 +4767,21 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K3 K5:K11" xr:uid="{18A2CFC6-B8F9-4089-AA92-007E36DE9D47}">
+      <formula1>"hindi,english,maths"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4862D149-6CC9-4AC2-9E4C-5C945327D7E5}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Excel9to10/Day-5.xlsx
+++ b/Excel9to10/Day-5.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AllData\Excel9to10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF1EF0E-4879-4250-BE17-010C4E0CC127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{357E30EE-0CDE-4A14-A416-85E37EF2CCA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{647DEF58-673A-4D42-A1E9-37071E949B6C}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="131">
   <si>
     <t>ID</t>
   </si>
@@ -447,6 +447,12 @@
   </si>
   <si>
     <t>Input</t>
+  </si>
+  <si>
+    <t>a1</t>
+  </si>
+  <si>
+    <t>R1C1</t>
   </si>
 </sst>
 </file>
@@ -505,12 +511,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -529,9 +536,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -569,7 +576,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -675,7 +682,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -817,7 +824,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -825,7 +832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F125F0B-8C0C-45C0-923A-98B0C145109C}">
-  <dimension ref="A1:W101"/>
+  <dimension ref="A1:V101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.85546875" customWidth="1"/>
@@ -1007,9 +1014,17 @@
       <c r="J5" s="1">
         <v>3660</v>
       </c>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1" t="str">
+        <f>IFERROR(VLOOKUP($L$5,$A$2:$J$101,2),"-")</f>
+        <v>John Smith</v>
+      </c>
+      <c r="N5" s="1">
+        <f>IFERROR(VLOOKUP($L$5,$A$2:$J$101,5),"-")</f>
+        <v>58000</v>
+      </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1201,43 +1216,43 @@
         <v>3600</v>
       </c>
       <c r="M10">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N10" t="str">
-        <f>_xlfn.XLOOKUP($M$10,$A$2:$A$101,B2:B101,"-")</f>
-        <v>Isabella Martinez</v>
+        <f>IFERROR(INDEX(B:B,MATCH($M$10,$A:$A,0)),"-")</f>
+        <v>John Smith</v>
       </c>
       <c r="O10" t="str">
-        <f>_xlfn.XLOOKUP($M$10,$A$2:$A$101,C2:C101,"-")</f>
-        <v>HR</v>
+        <f t="shared" ref="O10:V10" si="0">IFERROR(INDEX(C:C,MATCH($M$10,$A:$A,0)),"-")</f>
+        <v>Sales</v>
       </c>
       <c r="P10" t="str">
-        <f t="shared" ref="P10:V10" si="0">_xlfn.XLOOKUP($M$10,$A$2:$A$101,D2:D101,"-")</f>
-        <v>Chicago</v>
+        <f t="shared" si="0"/>
+        <v>New York</v>
       </c>
       <c r="Q10">
         <f t="shared" si="0"/>
-        <v>51000</v>
+        <v>58000</v>
       </c>
       <c r="R10">
         <f t="shared" si="0"/>
-        <v>43645</v>
+        <v>43171</v>
       </c>
       <c r="S10" t="str">
         <f t="shared" si="0"/>
-        <v>David</v>
+        <v>Alice</v>
       </c>
       <c r="T10">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U10">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <f t="shared" si="0"/>
-        <v>2550</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
@@ -1271,6 +1286,45 @@
       <c r="J11" s="1">
         <v>5840</v>
       </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11" t="str">
+        <f>_xlfn.XLOOKUP($M$11,$A:$A,B:B,"-",0,1)</f>
+        <v>John Smith</v>
+      </c>
+      <c r="O11" t="str">
+        <f t="shared" ref="O11:V11" si="1">_xlfn.XLOOKUP($M$11,$A:$A,C:C,"-",0,1)</f>
+        <v>Sales</v>
+      </c>
+      <c r="P11" t="str">
+        <f t="shared" si="1"/>
+        <v>New York</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="1"/>
+        <v>58000</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="1"/>
+        <v>43171</v>
+      </c>
+      <c r="S11" t="str">
+        <f t="shared" si="1"/>
+        <v>Alice</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="1"/>
+        <v>3480</v>
+      </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -1303,6 +1357,10 @@
       <c r="J12" s="1">
         <v>3420</v>
       </c>
+      <c r="L12" t="str">
+        <f ca="1">OFFSET(A2,3,1)</f>
+        <v>Emma Davis</v>
+      </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -1335,10 +1393,6 @@
       <c r="J13" s="1">
         <v>2500</v>
       </c>
-      <c r="L13">
-        <f>_xlfn.MODE.SNGL(E2:E101)</f>
-        <v>71000</v>
-      </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -1403,12 +1457,6 @@
       <c r="J15" s="1">
         <v>3720</v>
       </c>
-      <c r="N15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -1441,8 +1489,18 @@
       <c r="J16" s="1">
         <v>3550</v>
       </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L16" s="4">
+        <v>46132</v>
+      </c>
+      <c r="N16" t="e" cm="1">
+        <f t="array" aca="1" ref="N16" ca="1">INDIRECT(O16,)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="O16" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1473,8 +1531,15 @@
       <c r="J17" s="1">
         <v>3360</v>
       </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="O17" t="s">
+        <v>130</v>
+      </c>
+      <c r="P17" t="str" cm="1">
+        <f t="array" aca="1" ref="P17" ca="1">INDIRECT(O17,FALSE)</f>
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1505,39 +1570,11 @@
       <c r="J18" s="1">
         <v>5640</v>
       </c>
-      <c r="N18" cm="1">
-        <f t="array" ref="N18:W37">_xlfn._xlws.FILTER(A1:J101,D1:D101=O15,"-")</f>
-        <v>2</v>
-      </c>
-      <c r="O18" t="str">
-        <v>Sarah Lee</v>
-      </c>
-      <c r="P18" t="str">
-        <v>HR</v>
-      </c>
-      <c r="Q18" t="str">
-        <v>Chicago</v>
-      </c>
-      <c r="R18">
-        <v>52000</v>
-      </c>
-      <c r="S18">
-        <v>43647</v>
-      </c>
-      <c r="T18" t="str">
-        <v>David</v>
-      </c>
-      <c r="U18">
-        <v>3</v>
-      </c>
-      <c r="V18">
-        <v>5</v>
-      </c>
-      <c r="W18">
-        <v>2600</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L18" s="5">
+        <v>0.39374999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1568,38 +1605,8 @@
       <c r="J19" s="1">
         <v>2575</v>
       </c>
-      <c r="N19">
-        <v>8</v>
-      </c>
-      <c r="O19" t="str">
-        <v>Isabella Martinez</v>
-      </c>
-      <c r="P19" t="str">
-        <v>HR</v>
-      </c>
-      <c r="Q19" t="str">
-        <v>Chicago</v>
-      </c>
-      <c r="R19">
-        <v>51000</v>
-      </c>
-      <c r="S19">
-        <v>43645</v>
-      </c>
-      <c r="T19" t="str">
-        <v>David</v>
-      </c>
-      <c r="U19">
-        <v>3</v>
-      </c>
-      <c r="V19">
-        <v>5</v>
-      </c>
-      <c r="W19">
-        <v>2550</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1630,41 +1637,9 @@
       <c r="J20" s="1">
         <v>3630</v>
       </c>
-      <c r="L20" s="4">
-        <v>46058</v>
-      </c>
-      <c r="N20">
-        <v>12</v>
-      </c>
-      <c r="O20" t="str">
-        <v>Mia Walker</v>
-      </c>
-      <c r="P20" t="str">
-        <v>HR</v>
-      </c>
-      <c r="Q20" t="str">
-        <v>Chicago</v>
-      </c>
-      <c r="R20">
-        <v>50000</v>
-      </c>
-      <c r="S20">
-        <v>44025</v>
-      </c>
-      <c r="T20" t="str">
-        <v>David</v>
-      </c>
-      <c r="U20">
-        <v>3</v>
-      </c>
-      <c r="V20">
-        <v>5</v>
-      </c>
-      <c r="W20">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L20" s="4"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1695,38 +1670,8 @@
       <c r="J21" s="1">
         <v>5880</v>
       </c>
-      <c r="N21">
-        <v>18</v>
-      </c>
-      <c r="O21" t="str">
-        <v>Evelyn Wright</v>
-      </c>
-      <c r="P21" t="str">
-        <v>HR</v>
-      </c>
-      <c r="Q21" t="str">
-        <v>Chicago</v>
-      </c>
-      <c r="R21">
-        <v>51500</v>
-      </c>
-      <c r="S21">
-        <v>43739</v>
-      </c>
-      <c r="T21" t="str">
-        <v>David</v>
-      </c>
-      <c r="U21">
-        <v>3</v>
-      </c>
-      <c r="V21">
-        <v>5</v>
-      </c>
-      <c r="W21">
-        <v>2575</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1757,38 +1702,8 @@
       <c r="J22" s="1">
         <v>3510</v>
       </c>
-      <c r="N22">
-        <v>22</v>
-      </c>
-      <c r="O22" t="str">
-        <v>Amelia Green</v>
-      </c>
-      <c r="P22" t="str">
-        <v>HR</v>
-      </c>
-      <c r="Q22" t="str">
-        <v>Chicago</v>
-      </c>
-      <c r="R22">
-        <v>52500</v>
-      </c>
-      <c r="S22">
-        <v>43511</v>
-      </c>
-      <c r="T22" t="str">
-        <v>David</v>
-      </c>
-      <c r="U22">
-        <v>3</v>
-      </c>
-      <c r="V22">
-        <v>5</v>
-      </c>
-      <c r="W22">
-        <v>2625</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1819,38 +1734,8 @@
       <c r="J23" s="1">
         <v>2625</v>
       </c>
-      <c r="N23">
-        <v>28</v>
-      </c>
-      <c r="O23" t="str">
-        <v>Elizabeth Turner</v>
-      </c>
-      <c r="P23" t="str">
-        <v>HR</v>
-      </c>
-      <c r="Q23" t="str">
-        <v>Chicago</v>
-      </c>
-      <c r="R23">
-        <v>50500</v>
-      </c>
-      <c r="S23">
-        <v>43655</v>
-      </c>
-      <c r="T23" t="str">
-        <v>David</v>
-      </c>
-      <c r="U23">
-        <v>3</v>
-      </c>
-      <c r="V23">
-        <v>5</v>
-      </c>
-      <c r="W23">
-        <v>2525</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1881,38 +1766,8 @@
       <c r="J24" s="1">
         <v>5400</v>
       </c>
-      <c r="N24">
-        <v>32</v>
-      </c>
-      <c r="O24" t="str">
-        <v>Sofia Evans</v>
-      </c>
-      <c r="P24" t="str">
-        <v>HR</v>
-      </c>
-      <c r="Q24" t="str">
-        <v>Chicago</v>
-      </c>
-      <c r="R24">
-        <v>53000</v>
-      </c>
-      <c r="S24">
-        <v>44079</v>
-      </c>
-      <c r="T24" t="str">
-        <v>David</v>
-      </c>
-      <c r="U24">
-        <v>3</v>
-      </c>
-      <c r="V24">
-        <v>5</v>
-      </c>
-      <c r="W24">
-        <v>2650</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1943,38 +1798,8 @@
       <c r="J25" s="1">
         <v>3690</v>
       </c>
-      <c r="N25">
-        <v>38</v>
-      </c>
-      <c r="O25" t="str">
-        <v>Grace Rogers</v>
-      </c>
-      <c r="P25" t="str">
-        <v>HR</v>
-      </c>
-      <c r="Q25" t="str">
-        <v>Chicago</v>
-      </c>
-      <c r="R25">
-        <v>52000</v>
-      </c>
-      <c r="S25">
-        <v>43627</v>
-      </c>
-      <c r="T25" t="str">
-        <v>David</v>
-      </c>
-      <c r="U25">
-        <v>3</v>
-      </c>
-      <c r="V25">
-        <v>5</v>
-      </c>
-      <c r="W25">
-        <v>2600</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -2005,38 +1830,8 @@
       <c r="J26" s="1">
         <v>3625</v>
       </c>
-      <c r="N26">
-        <v>42</v>
-      </c>
-      <c r="O26" t="str">
-        <v>Hazel Bell</v>
-      </c>
-      <c r="P26" t="str">
-        <v>HR</v>
-      </c>
-      <c r="Q26" t="str">
-        <v>Chicago</v>
-      </c>
-      <c r="R26">
-        <v>53500</v>
-      </c>
-      <c r="S26">
-        <v>43669</v>
-      </c>
-      <c r="T26" t="str">
-        <v>David</v>
-      </c>
-      <c r="U26">
-        <v>3</v>
-      </c>
-      <c r="V26">
-        <v>5</v>
-      </c>
-      <c r="W26">
-        <v>2675</v>
-      </c>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -2067,38 +1862,8 @@
       <c r="J27" s="1">
         <v>3270</v>
       </c>
-      <c r="N27">
-        <v>48</v>
-      </c>
-      <c r="O27" t="str">
-        <v>Nora Cox</v>
-      </c>
-      <c r="P27" t="str">
-        <v>HR</v>
-      </c>
-      <c r="Q27" t="str">
-        <v>Chicago</v>
-      </c>
-      <c r="R27">
-        <v>51000</v>
-      </c>
-      <c r="S27">
-        <v>43696</v>
-      </c>
-      <c r="T27" t="str">
-        <v>David</v>
-      </c>
-      <c r="U27">
-        <v>3</v>
-      </c>
-      <c r="V27">
-        <v>5</v>
-      </c>
-      <c r="W27">
-        <v>2550</v>
-      </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -2129,38 +1894,11 @@
       <c r="J28" s="1">
         <v>5560</v>
       </c>
-      <c r="N28">
-        <v>52</v>
-      </c>
-      <c r="O28" t="str">
-        <v>Penelope Torres</v>
-      </c>
-      <c r="P28" t="str">
-        <v>HR</v>
-      </c>
-      <c r="Q28" t="str">
-        <v>Chicago</v>
-      </c>
-      <c r="R28">
-        <v>54000</v>
-      </c>
-      <c r="S28">
-        <v>43600</v>
-      </c>
-      <c r="T28" t="str">
-        <v>David</v>
-      </c>
-      <c r="U28">
-        <v>3</v>
-      </c>
-      <c r="V28">
-        <v>5</v>
-      </c>
-      <c r="W28">
-        <v>2700</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L28">
+        <v>0.4856476387228198</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -2191,38 +1929,8 @@
       <c r="J29" s="1">
         <v>2525</v>
       </c>
-      <c r="N29">
-        <v>58</v>
-      </c>
-      <c r="O29" t="str">
-        <v>Eleanor Foster</v>
-      </c>
-      <c r="P29" t="str">
-        <v>HR</v>
-      </c>
-      <c r="Q29" t="str">
-        <v>Chicago</v>
-      </c>
-      <c r="R29">
-        <v>51500</v>
-      </c>
-      <c r="S29">
-        <v>43726</v>
-      </c>
-      <c r="T29" t="str">
-        <v>David</v>
-      </c>
-      <c r="U29">
-        <v>3</v>
-      </c>
-      <c r="V29">
-        <v>5</v>
-      </c>
-      <c r="W29">
-        <v>2575</v>
-      </c>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -2253,38 +1961,8 @@
       <c r="J30" s="1">
         <v>3660</v>
       </c>
-      <c r="N30">
-        <v>62</v>
-      </c>
-      <c r="O30" t="str">
-        <v>Lucy Rivera</v>
-      </c>
-      <c r="P30" t="str">
-        <v>HR</v>
-      </c>
-      <c r="Q30" t="str">
-        <v>Chicago</v>
-      </c>
-      <c r="R30">
-        <v>53000</v>
-      </c>
-      <c r="S30">
-        <v>43704</v>
-      </c>
-      <c r="T30" t="str">
-        <v>David</v>
-      </c>
-      <c r="U30">
-        <v>3</v>
-      </c>
-      <c r="V30">
-        <v>5</v>
-      </c>
-      <c r="W30">
-        <v>2650</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -2315,38 +1993,8 @@
       <c r="J31" s="1">
         <v>5920</v>
       </c>
-      <c r="N31">
-        <v>68</v>
-      </c>
-      <c r="O31" t="str">
-        <v>Eva Coleman</v>
-      </c>
-      <c r="P31" t="str">
-        <v>HR</v>
-      </c>
-      <c r="Q31" t="str">
-        <v>Chicago</v>
-      </c>
-      <c r="R31">
-        <v>50500</v>
-      </c>
-      <c r="S31">
-        <v>43740</v>
-      </c>
-      <c r="T31" t="str">
-        <v>David</v>
-      </c>
-      <c r="U31">
-        <v>3</v>
-      </c>
-      <c r="V31">
-        <v>5</v>
-      </c>
-      <c r="W31">
-        <v>2525</v>
-      </c>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -2375,40 +2023,14 @@
         <v>6</v>
       </c>
       <c r="J32" s="1">
-        <v>3450</v>
-      </c>
-      <c r="N32">
-        <v>72</v>
-      </c>
-      <c r="O32" t="str">
-        <v>Lillian Patterson</v>
-      </c>
-      <c r="P32" t="str">
-        <v>HR</v>
-      </c>
-      <c r="Q32" t="str">
-        <v>Chicago</v>
-      </c>
-      <c r="R32">
-        <v>51500</v>
-      </c>
-      <c r="S32">
-        <v>43625</v>
-      </c>
-      <c r="T32" t="str">
-        <v>David</v>
-      </c>
-      <c r="U32">
-        <v>3</v>
-      </c>
-      <c r="V32">
-        <v>5</v>
-      </c>
-      <c r="W32">
-        <v>2575</v>
-      </c>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+      <c r="L32">
+        <f ca="1">RAND()</f>
+        <v>0.3252601691779492</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -2439,38 +2061,8 @@
       <c r="J33" s="1">
         <v>2650</v>
       </c>
-      <c r="N33">
-        <v>78</v>
-      </c>
-      <c r="O33" t="str">
-        <v>Bella Hughes</v>
-      </c>
-      <c r="P33" t="str">
-        <v>HR</v>
-      </c>
-      <c r="Q33" t="str">
-        <v>Chicago</v>
-      </c>
-      <c r="R33">
-        <v>52000</v>
-      </c>
-      <c r="S33">
-        <v>43711</v>
-      </c>
-      <c r="T33" t="str">
-        <v>David</v>
-      </c>
-      <c r="U33">
-        <v>3</v>
-      </c>
-      <c r="V33">
-        <v>5</v>
-      </c>
-      <c r="W33">
-        <v>2600</v>
-      </c>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -2501,38 +2093,8 @@
       <c r="J34" s="1">
         <v>5440</v>
       </c>
-      <c r="N34">
-        <v>82</v>
-      </c>
-      <c r="O34" t="str">
-        <v>Clara Rivera</v>
-      </c>
-      <c r="P34" t="str">
-        <v>HR</v>
-      </c>
-      <c r="Q34" t="str">
-        <v>Chicago</v>
-      </c>
-      <c r="R34">
-        <v>53000</v>
-      </c>
-      <c r="S34">
-        <v>43665</v>
-      </c>
-      <c r="T34" t="str">
-        <v>David</v>
-      </c>
-      <c r="U34">
-        <v>3</v>
-      </c>
-      <c r="V34">
-        <v>5</v>
-      </c>
-      <c r="W34">
-        <v>2650</v>
-      </c>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -2563,38 +2125,12 @@
       <c r="J35" s="1">
         <v>3750</v>
       </c>
-      <c r="N35">
-        <v>88</v>
-      </c>
-      <c r="O35" t="str">
-        <v>Sadie Henderson</v>
-      </c>
-      <c r="P35" t="str">
-        <v>HR</v>
-      </c>
-      <c r="Q35" t="str">
-        <v>Chicago</v>
-      </c>
-      <c r="R35">
-        <v>51000</v>
-      </c>
-      <c r="S35">
-        <v>43637</v>
-      </c>
-      <c r="T35" t="str">
-        <v>David</v>
-      </c>
-      <c r="U35">
-        <v>3</v>
-      </c>
-      <c r="V35">
-        <v>5</v>
-      </c>
-      <c r="W35">
-        <v>2550</v>
-      </c>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L35">
+        <f ca="1">RANDBETWEEN(12,16)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -2625,38 +2161,8 @@
       <c r="J36" s="1">
         <v>3575</v>
       </c>
-      <c r="N36">
-        <v>92</v>
-      </c>
-      <c r="O36" t="str">
-        <v>Nora Reynolds</v>
-      </c>
-      <c r="P36" t="str">
-        <v>HR</v>
-      </c>
-      <c r="Q36" t="str">
-        <v>Chicago</v>
-      </c>
-      <c r="R36">
-        <v>52500</v>
-      </c>
-      <c r="S36">
-        <v>43682</v>
-      </c>
-      <c r="T36" t="str">
-        <v>David</v>
-      </c>
-      <c r="U36">
-        <v>3</v>
-      </c>
-      <c r="V36">
-        <v>5</v>
-      </c>
-      <c r="W36">
-        <v>2625</v>
-      </c>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -2687,38 +2193,8 @@
       <c r="J37" s="1">
         <v>3300</v>
       </c>
-      <c r="N37">
-        <v>98</v>
-      </c>
-      <c r="O37" t="str">
-        <v>Maya Graham</v>
-      </c>
-      <c r="P37" t="str">
-        <v>HR</v>
-      </c>
-      <c r="Q37" t="str">
-        <v>Chicago</v>
-      </c>
-      <c r="R37">
-        <v>50500</v>
-      </c>
-      <c r="S37">
-        <v>43632</v>
-      </c>
-      <c r="T37" t="str">
-        <v>David</v>
-      </c>
-      <c r="U37">
-        <v>3</v>
-      </c>
-      <c r="V37">
-        <v>5</v>
-      </c>
-      <c r="W37">
-        <v>2525</v>
-      </c>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -2749,8 +2225,39 @@
       <c r="J38" s="1">
         <v>5680</v>
       </c>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L38" cm="1">
+        <f t="array" ref="L38:U47">_xlfn._xlws.FILTER(A1:J101,D1:D101=D31,"-")</f>
+        <v>10</v>
+      </c>
+      <c r="M38" t="str">
+        <v>Ava Rodriguez</v>
+      </c>
+      <c r="N38" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="O38" t="str">
+        <v>Phoenix</v>
+      </c>
+      <c r="P38">
+        <v>73000</v>
+      </c>
+      <c r="Q38">
+        <v>42844</v>
+      </c>
+      <c r="R38" t="str">
+        <v>John</v>
+      </c>
+      <c r="S38">
+        <v>5</v>
+      </c>
+      <c r="T38">
+        <v>8</v>
+      </c>
+      <c r="U38">
+        <v>5840</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -2781,8 +2288,38 @@
       <c r="J39" s="1">
         <v>2600</v>
       </c>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L39">
+        <v>20</v>
+      </c>
+      <c r="M39" t="str">
+        <v>Sophia Hill</v>
+      </c>
+      <c r="N39" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="O39" t="str">
+        <v>Phoenix</v>
+      </c>
+      <c r="P39">
+        <v>73500</v>
+      </c>
+      <c r="Q39">
+        <v>42935</v>
+      </c>
+      <c r="R39" t="str">
+        <v>John</v>
+      </c>
+      <c r="S39">
+        <v>5</v>
+      </c>
+      <c r="T39">
+        <v>8</v>
+      </c>
+      <c r="U39">
+        <v>5880</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -2813,8 +2350,38 @@
       <c r="J40" s="1">
         <v>3630</v>
       </c>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L40">
+        <v>30</v>
+      </c>
+      <c r="M40" t="str">
+        <v>Victoria Campbell</v>
+      </c>
+      <c r="N40" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="O40" t="str">
+        <v>Phoenix</v>
+      </c>
+      <c r="P40">
+        <v>74000</v>
+      </c>
+      <c r="Q40">
+        <v>42819</v>
+      </c>
+      <c r="R40" t="str">
+        <v>John</v>
+      </c>
+      <c r="S40">
+        <v>5</v>
+      </c>
+      <c r="T40">
+        <v>8</v>
+      </c>
+      <c r="U40">
+        <v>5920</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -2845,8 +2412,38 @@
       <c r="J41" s="1">
         <v>5960</v>
       </c>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L41">
+        <v>40</v>
+      </c>
+      <c r="M41" t="str">
+        <v>Scarlett Cook</v>
+      </c>
+      <c r="N41" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="O41" t="str">
+        <v>Phoenix</v>
+      </c>
+      <c r="P41">
+        <v>74500</v>
+      </c>
+      <c r="Q41">
+        <v>42781</v>
+      </c>
+      <c r="R41" t="str">
+        <v>John</v>
+      </c>
+      <c r="S41">
+        <v>5</v>
+      </c>
+      <c r="T41">
+        <v>8</v>
+      </c>
+      <c r="U41">
+        <v>5960</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -2877,8 +2474,38 @@
       <c r="J42" s="1">
         <v>3390</v>
       </c>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L42">
+        <v>50</v>
+      </c>
+      <c r="M42" t="str">
+        <v>Zoe Ward</v>
+      </c>
+      <c r="N42" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="O42" t="str">
+        <v>Phoenix</v>
+      </c>
+      <c r="P42">
+        <v>75000</v>
+      </c>
+      <c r="Q42">
+        <v>42896</v>
+      </c>
+      <c r="R42" t="str">
+        <v>John</v>
+      </c>
+      <c r="S42">
+        <v>5</v>
+      </c>
+      <c r="T42">
+        <v>8</v>
+      </c>
+      <c r="U42">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -2909,8 +2536,38 @@
       <c r="J43" s="1">
         <v>2675</v>
       </c>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L43">
+        <v>60</v>
+      </c>
+      <c r="M43" t="str">
+        <v>Avery Bennett</v>
+      </c>
+      <c r="N43" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="O43" t="str">
+        <v>Phoenix</v>
+      </c>
+      <c r="P43">
+        <v>75500</v>
+      </c>
+      <c r="Q43">
+        <v>42822</v>
+      </c>
+      <c r="R43" t="str">
+        <v>John</v>
+      </c>
+      <c r="S43">
+        <v>5</v>
+      </c>
+      <c r="T43">
+        <v>8</v>
+      </c>
+      <c r="U43">
+        <v>6040</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -2941,8 +2598,38 @@
       <c r="J44" s="1">
         <v>5480</v>
       </c>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L44">
+        <v>70</v>
+      </c>
+      <c r="M44" t="str">
+        <v>Aurora Perry</v>
+      </c>
+      <c r="N44" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="O44" t="str">
+        <v>Phoenix</v>
+      </c>
+      <c r="P44">
+        <v>76000</v>
+      </c>
+      <c r="Q44">
+        <v>42869</v>
+      </c>
+      <c r="R44" t="str">
+        <v>John</v>
+      </c>
+      <c r="S44">
+        <v>5</v>
+      </c>
+      <c r="T44">
+        <v>8</v>
+      </c>
+      <c r="U44">
+        <v>6080</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -2973,8 +2660,38 @@
       <c r="J45" s="1">
         <v>3780</v>
       </c>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L45">
+        <v>80</v>
+      </c>
+      <c r="M45" t="str">
+        <v>Naomi Flores</v>
+      </c>
+      <c r="N45" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="O45" t="str">
+        <v>Phoenix</v>
+      </c>
+      <c r="P45">
+        <v>74000</v>
+      </c>
+      <c r="Q45">
+        <v>42815</v>
+      </c>
+      <c r="R45" t="str">
+        <v>John</v>
+      </c>
+      <c r="S45">
+        <v>5</v>
+      </c>
+      <c r="T45">
+        <v>8</v>
+      </c>
+      <c r="U45">
+        <v>5920</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -3005,8 +2722,38 @@
       <c r="J46" s="1">
         <v>3525</v>
       </c>
-    </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L46">
+        <v>90</v>
+      </c>
+      <c r="M46" t="str">
+        <v>Alice Fisher</v>
+      </c>
+      <c r="N46" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="O46" t="str">
+        <v>Phoenix</v>
+      </c>
+      <c r="P46">
+        <v>75500</v>
+      </c>
+      <c r="Q46">
+        <v>42830</v>
+      </c>
+      <c r="R46" t="str">
+        <v>John</v>
+      </c>
+      <c r="S46">
+        <v>5</v>
+      </c>
+      <c r="T46">
+        <v>8</v>
+      </c>
+      <c r="U46">
+        <v>6040</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -3037,8 +2784,38 @@
       <c r="J47" s="1">
         <v>3330</v>
       </c>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="L47">
+        <v>100</v>
+      </c>
+      <c r="M47" t="str">
+        <v>Samantha Olson</v>
+      </c>
+      <c r="N47" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="O47" t="str">
+        <v>Phoenix</v>
+      </c>
+      <c r="P47">
+        <v>75000</v>
+      </c>
+      <c r="Q47">
+        <v>42873</v>
+      </c>
+      <c r="R47" t="str">
+        <v>John</v>
+      </c>
+      <c r="S47">
+        <v>5</v>
+      </c>
+      <c r="T47">
+        <v>8</v>
+      </c>
+      <c r="U47">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -4767,21 +4544,23 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K3 K5:K11" xr:uid="{18A2CFC6-B8F9-4089-AA92-007E36DE9D47}">
-      <formula1>"hindi,english,maths"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4862D149-6CC9-4AC2-9E4C-5C945327D7E5}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CB525EC-D01E-4DA8-A0E7-08AE9A539511}">
+  <dimension ref="B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" t="str">
+        <f>VLOOKUP(1,Sheet1!A2:J101,2)</f>
+        <v>John Smith</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>